--- a/anexo_1.xlsx
+++ b/anexo_1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yunior\Desktop\programa5\costousd\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yunior\Desktop\Nueva carpeta (4)\programa5\costousd\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
   <si>
     <t>ANEXO 1</t>
   </si>
@@ -144,15 +144,6 @@
   </si>
   <si>
     <t>Pimienta negra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tener en dispuestos los ingredientes a utilizar así como los utensilios de trabajo. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moler los diferentes géneros ,sofreir las especies , mezclar todo y conformar la hamburguesa. </t>
-  </si>
-  <si>
-    <t>Servir en plato para  ensalada y decorar.</t>
   </si>
   <si>
     <t>NOMBRE DEL PLATO A ELABORAR: Hamburguesa Taína</t>
@@ -685,45 +676,7 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -750,6 +703,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -795,7 +749,44 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1124,23 +1115,23 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="62" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="H3" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
+      <c r="B4" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="4"/>
@@ -1148,25 +1139,25 @@
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="43" t="s">
+      <c r="H5" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="8"/>
@@ -1175,8 +1166,8 @@
       <c r="G6" s="8"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
       <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -1209,46 +1200,46 @@
       <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="71" t="s">
+      <c r="E9" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="72"/>
-      <c r="G9" s="73" t="s">
+      <c r="F9" s="61"/>
+      <c r="G9" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="75" t="s">
+      <c r="H9" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="76" t="s">
+      <c r="I9" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="77"/>
+      <c r="J9" s="66"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="68"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
       <c r="E10" s="14" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="74"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="76" t="s">
+      <c r="G10" s="63"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="77"/>
+      <c r="J10" s="66"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16"/>
@@ -1273,10 +1264,8 @@
       <c r="H11" s="37">
         <v>2.0133999999999999</v>
       </c>
-      <c r="I11" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="57"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="45"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
@@ -1301,8 +1290,8 @@
       <c r="H12" s="37">
         <v>0.312</v>
       </c>
-      <c r="I12" s="58"/>
-      <c r="J12" s="59"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="47"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
@@ -1327,8 +1316,8 @@
       <c r="H13" s="37">
         <v>1.0713999999999999</v>
       </c>
-      <c r="I13" s="58"/>
-      <c r="J13" s="59"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16"/>
@@ -1353,8 +1342,8 @@
       <c r="H14" s="37">
         <v>9.6999999999999993</v>
       </c>
-      <c r="I14" s="60"/>
-      <c r="J14" s="61"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16"/>
@@ -1379,10 +1368,10 @@
       <c r="H15" s="37">
         <v>6.8624999999999998</v>
       </c>
-      <c r="I15" s="54" t="s">
+      <c r="I15" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="55"/>
+      <c r="J15" s="68"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
@@ -1407,10 +1396,8 @@
       <c r="H16" s="37">
         <v>7.12</v>
       </c>
-      <c r="I16" s="56" t="s">
-        <v>41</v>
-      </c>
-      <c r="J16" s="57"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
@@ -1435,8 +1422,8 @@
       <c r="H17" s="37">
         <v>0.90300000000000002</v>
       </c>
-      <c r="I17" s="58"/>
-      <c r="J17" s="59"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
@@ -1461,8 +1448,8 @@
       <c r="H18" s="37">
         <v>0.54349999999999998</v>
       </c>
-      <c r="I18" s="60"/>
-      <c r="J18" s="61"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
@@ -1487,10 +1474,10 @@
       <c r="H19" s="37">
         <v>1.09E-2</v>
       </c>
-      <c r="I19" s="54" t="s">
+      <c r="I19" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="J19" s="55"/>
+      <c r="J19" s="68"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B20" s="20">
@@ -1514,10 +1501,8 @@
       <c r="H20" s="37">
         <v>0.18010000000000001</v>
       </c>
-      <c r="I20" s="56" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="57"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="45"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="20"/>
@@ -1526,8 +1511,8 @@
       <c r="E21" s="37"/>
       <c r="F21" s="37"/>
       <c r="G21" s="40"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="61"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="49"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="20"/>
@@ -1537,10 +1522,10 @@
       <c r="F22" s="37"/>
       <c r="G22" s="40"/>
       <c r="H22" s="37"/>
-      <c r="I22" s="54" t="s">
+      <c r="I22" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="55"/>
+      <c r="J22" s="68"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B23" s="20"/>
@@ -1565,15 +1550,15 @@
       <c r="J24" s="25"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="46"/>
+      <c r="B25" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="71"/>
       <c r="I25" s="37">
         <f>SUM(H11:H24)</f>
         <v>28.716799999999999</v>
@@ -1584,7 +1569,7 @@
     </row>
     <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H26" s="26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I26" s="27">
         <f>(5/100*I25)</f>
@@ -1609,11 +1594,11 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
       <c r="E29" s="27">
         <f>I27</f>
         <v>30.152639999999998</v>
@@ -1625,20 +1610,20 @@
       <c r="L29" s="30"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="78">
+      <c r="C30" s="75"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="43">
         <f>ROUNDUP((E32+E31)/5,0)*5</f>
         <v>265</v>
       </c>
-      <c r="G30" s="51" t="s">
+      <c r="G30" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="78"/>
       <c r="J30" s="31">
         <f>I27/E30</f>
         <v>0.11378354716981132</v>
@@ -1646,35 +1631,35 @@
       <c r="L30" s="32"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="78">
+      <c r="B31" s="74" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="43">
         <f>(10/100*E32)</f>
         <v>24</v>
       </c>
-      <c r="G31" s="53"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="53"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
       <c r="L31" s="32"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="78">
+      <c r="B32" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="75"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="43">
         <v>240</v>
       </c>
       <c r="L32" s="31"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="49"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="75"/>
       <c r="E33" s="3"/>
       <c r="F33" s="11"/>
       <c r="G33" s="33"/>
@@ -1693,41 +1678,41 @@
       <c r="H34" s="34"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
+      <c r="B35" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="43" t="s">
+      <c r="B39" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43" t="s">
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43" t="s">
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="K39" s="43"/>
+      <c r="K39" s="54"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D40" s="8"/>
@@ -1738,6 +1723,24 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F36:G38"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J21"/>
+    <mergeCell ref="I22:J22"/>
     <mergeCell ref="I11:J14"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="B4:G4"/>
@@ -1752,24 +1755,6 @@
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J18"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F36:G38"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G30:I30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
